--- a/marketing_forms/001_signup_form--marketing_forms.xlsx
+++ b/marketing_forms/001_signup_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
